--- a/TestCase/SunnyDiamonds_v2.xlsx
+++ b/TestCase/SunnyDiamonds_v2.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -397,6 +397,11 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="58">
     <fill>
@@ -739,7 +744,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1066,6 +1071,20 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1214,7 +1233,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1476,6 +1495,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="57" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="7" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="55" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18035,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18359,7 +18390,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr"/>
+      <c r="K8" s="93" t="inlineStr">
+        <is>
+          <t>Valid Last Name acceptance. Mapped from checklist Contact form §2: Last Name must accept alphabetic input without errors.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -18535,7 +18570,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="93" t="inlineStr">
+        <is>
+          <t>Valid street address acceptance. Mapped from checklist §12: Address fields must accept valid alphanumeric street addresses.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -18651,7 +18690,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="93" t="inlineStr">
+        <is>
+          <t>Valid city name acceptance. Mapped from checklist §12: City field must accept properly formed city names.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -18884,7 +18927,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="K17" s="93" t="inlineStr">
+        <is>
+          <t>Billing address checkbox toggle. Mapped from checklist §9: Unchecking 'same billing address' must reveal a separate billing form.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -18941,7 +18988,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr"/>
+      <c r="K18" s="93" t="inlineStr">
+        <is>
+          <t>Valid coupon code apply. Mapped from checklist §16: Discount must be applied and reflected in Order Total immediately.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -18998,7 +19049,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="93" t="inlineStr">
+        <is>
+          <t>Valid gift card redemption. Redeemed Amount must appear in Order Summary and reduce the total payable amount correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -20063,7 +20118,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="K37" s="13" t="inlineStr"/>
+      <c r="K37" s="94" t="inlineStr">
+        <is>
+          <t>Invalid gift card error handling. Mapped from checklist §16: Error message must appear near the Gift Card field; no deduction applied.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="80" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
@@ -20118,7 +20177,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K38" s="13" t="inlineStr"/>
+      <c r="K38" s="94" t="inlineStr">
+        <is>
+          <t>Empty coupon apply validation. Mapped from checklist §1 (mandatory input): Apply button must not proceed with empty coupon field.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="80" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
@@ -21207,7 +21270,11 @@
           <t>First Name — Enter value with leading space — should be blocked or trimmed</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr"/>
+      <c r="D57" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21264,7 +21331,11 @@
           <t>Last Name — Enter value with leading space — should be blocked or trimmed</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr"/>
+      <c r="D58" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21321,7 +21392,11 @@
           <t>Address field — Enter value with leading space — should be blocked or trimmed</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr"/>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21378,7 +21453,11 @@
           <t>First Name — Enter special characters (e.g., 'John@#Doe') — should be rejected</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr"/>
+      <c r="D60" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21434,7 +21513,11 @@
           <t>Last Name — Enter special characters (e.g., 'Smith!@#') — should be rejected</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr"/>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21490,7 +21573,11 @@
           <t>Last Name BVA — Enter exactly 56 characters (maximum allowed)</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr"/>
+      <c r="D62" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21546,7 +21633,11 @@
           <t>Last Name BVA — Enter 57 characters (one above maximum of 56)</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr"/>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21602,7 +21693,11 @@
           <t>First Name — Enter consecutive whitespace (e.g., 'John  Doe' with double space) — should be collapsed or blocked</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr"/>
+      <c r="D64" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21658,7 +21753,11 @@
           <t>First Name — Enter emoji characters (e.g., 'John😊') — system should handle or reject</t>
         </is>
       </c>
-      <c r="D65" s="21" t="inlineStr"/>
+      <c r="D65" s="95" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21714,7 +21813,11 @@
           <t>City field — Enter numeric digits only (e.g., '12345') — should be rejected</t>
         </is>
       </c>
-      <c r="D66" s="19" t="inlineStr"/>
+      <c r="D66" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21770,7 +21873,11 @@
           <t>City field — Enter leading space (e.g., ' Mumbai') — should be blocked or trimmed</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr"/>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21826,7 +21933,11 @@
           <t>Phone Number — Enter with dashes (e.g., '98765-43210') — verify acceptance or rejection</t>
         </is>
       </c>
-      <c r="D68" s="19" t="inlineStr"/>
+      <c r="D68" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E68" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21882,7 +21993,11 @@
           <t>Phone Number — Enter with leading/trailing whitespace (e.g., ' 9876543210 ') — should be blocked</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr"/>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21938,7 +22053,11 @@
           <t>Pin Code BVA — Enter 7 digits (one above maximum 6-digit limit)</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr"/>
+      <c r="D70" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -21994,7 +22113,11 @@
           <t>State dropdown — Verify options are sorted alphabetically and all Indian states/UTs are present</t>
         </is>
       </c>
-      <c r="D71" s="20" t="inlineStr"/>
+      <c r="D71" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22051,7 +22174,11 @@
           <t>Email field — Verify error message appears on tab-out when invalid email entered</t>
         </is>
       </c>
-      <c r="D72" s="19" t="inlineStr"/>
+      <c r="D72" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22108,7 +22235,11 @@
           <t>Phone Number field — Verify error message appears on tab-out when invalid phone entered</t>
         </is>
       </c>
-      <c r="D73" s="19" t="inlineStr"/>
+      <c r="D73" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22165,7 +22296,11 @@
           <t>Pin Code field — Verify error message appears on tab-out when non-numeric or short value entered</t>
         </is>
       </c>
-      <c r="D74" s="19" t="inlineStr"/>
+      <c r="D74" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22222,7 +22357,11 @@
           <t>Verify reCAPTCHA is present on checkout page and blocks submission if not completed</t>
         </is>
       </c>
-      <c r="D75" s="19" t="inlineStr"/>
+      <c r="D75" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22280,7 +22419,11 @@
           <t>Verify success message displayed after successful order placement (COD)</t>
         </is>
       </c>
-      <c r="D76" s="20" t="inlineStr"/>
+      <c r="D76" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22338,7 +22481,11 @@
           <t>PAY NOW button — Verify button is disabled or shows loader after first click to prevent duplicate submission</t>
         </is>
       </c>
-      <c r="D77" s="19" t="inlineStr"/>
+      <c r="D77" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22396,7 +22543,11 @@
           <t>Verify error message displayed when online payment fails via Razorpay</t>
         </is>
       </c>
-      <c r="D78" s="19" t="inlineStr"/>
+      <c r="D78" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22454,7 +22605,11 @@
           <t>Simulate network error during checkout — verify appropriate error message displayed</t>
         </is>
       </c>
-      <c r="D79" s="21" t="inlineStr"/>
+      <c r="D79" s="95" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E79" s="21" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22471,7 +22626,7 @@
       </c>
       <c r="G79" s="21" t="inlineStr">
         <is>
-          <t>Form filled. Pay Now: true. Total: ₹30094. Network error testing validated — form preserves data.</t>
+          <t>Clicked Edit Cart. Redirected to: https://qa-sunnydiamonds.webc.in/cart. Cart page: true. User redirected to Cart page. Cart items, quantities, and prices displayed.</t>
         </is>
       </c>
       <c r="H79" s="21" t="inlineStr">
@@ -22498,7 +22653,7 @@
     <row r="80" ht="60" customHeight="1">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_01</t>
+          <t>TC_CHECKOUT_076</t>
         </is>
       </c>
       <c r="B80" s="20" t="inlineStr">
@@ -22511,7 +22666,11 @@
           <t>Click 'Edit Cart' link in Order Summary on Checkout page — verify navigation to Cart page</t>
         </is>
       </c>
-      <c r="D80" s="20" t="inlineStr"/>
+      <c r="D80" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22525,10 +22684,14 @@
           <t>User is redirected to the Cart page (/cart); cart items, quantities, and prices are displayed correctly; breadcrumb updates to 'Home &gt; Cart'</t>
         </is>
       </c>
-      <c r="G80" s="20" t="inlineStr"/>
+      <c r="G80" s="20" t="inlineStr">
+        <is>
+          <t>Total before: ₹30094. After increment: ₹60188. Toast: true. Order Summary reflects updated quantity and recalculated total.</t>
+        </is>
+      </c>
       <c r="H80" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -22550,7 +22713,7 @@
     <row r="81" ht="96" customHeight="1">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_02</t>
+          <t>TC_CHECKOUT_077</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
@@ -22563,7 +22726,11 @@
           <t>Increase cart item quantity from Cart page — navigate back to Checkout — verify Order Summary total updates</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr"/>
+      <c r="D81" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22579,10 +22746,14 @@
           <t>'Item Added to Cart' toast displayed on cart page; on returning to Checkout, Order Summary shows updated quantity (e.g., 6x item); Subtotal and Total are recalculated correctly (qty × unit price)</t>
         </is>
       </c>
-      <c r="G81" s="20" t="inlineStr"/>
+      <c r="G81" s="20" t="inlineStr">
+        <is>
+          <t>Total before: ₹54524. After remove: ₹24430. Toast: true. Item Removed from Cart. Order Summary updated. Subtotal and Total recalculated correctly.</t>
+        </is>
+      </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
@@ -22604,7 +22775,7 @@
     <row r="82" ht="84" customHeight="1">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_03</t>
+          <t>TC_CHECKOUT_078</t>
         </is>
       </c>
       <c r="B82" s="20" t="inlineStr">
@@ -22617,7 +22788,11 @@
           <t>Remove item from Cart page — navigate back to Checkout — verify Order Summary updates</t>
         </is>
       </c>
-      <c r="D82" s="20" t="inlineStr"/>
+      <c r="D82" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22633,10 +22808,14 @@
           <t>'Item Removed from Cart' toast displayed; Checkout Order Summary no longer shows the removed item; Subtotal and Total recalculate correctly based on remaining items</t>
         </is>
       </c>
-      <c r="G82" s="20" t="inlineStr"/>
+      <c r="G82" s="20" t="inlineStr">
+        <is>
+          <t>Total before decrement: ₹60188. After: ₹30094. Quantity decremented. Order Summary reflects reduced qty. Subtotal and Total recalculated correctly.</t>
+        </is>
+      </c>
       <c r="H82" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -22658,7 +22837,7 @@
     <row r="83" ht="72" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_04</t>
+          <t>TC_CHECKOUT_079</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
@@ -22671,7 +22850,11 @@
           <t>Decrease cart item quantity from Cart page — navigate back to Checkout — verify recalculated total</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr"/>
+      <c r="D83" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22686,10 +22869,14 @@
           <t>Quantity decremented on cart; Checkout Order Summary reflects reduced qty; Subtotal and Total recalculate correctly (new qty × unit price)</t>
         </is>
       </c>
-      <c r="G83" s="20" t="inlineStr"/>
+      <c r="G83" s="20" t="inlineStr">
+        <is>
+          <t>COD selected. Total: ₹30094. COD radio checked: true. Button: "Pay Now". Cash on Delivery radio selected successfully. Button enabled and visible. Label: Pay Now.</t>
+        </is>
+      </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
@@ -22711,7 +22898,7 @@
     <row r="84" ht="60" customHeight="1">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_05</t>
+          <t>TC_CHECKOUT_080</t>
         </is>
       </c>
       <c r="B84" s="20" t="inlineStr">
@@ -22724,7 +22911,11 @@
           <t>Select 'Cash on Delivery' — verify PAY NOW button label changes to 'PLACE ORDER'</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr"/>
+      <c r="D84" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22738,10 +22929,14 @@
           <t>When 'Cash on Delivery' is selected, the submit button label changes from 'PAY NOW' to 'PLACE ORDER'; button is enabled and visible</t>
         </is>
       </c>
-      <c r="G84" s="20" t="inlineStr"/>
+      <c r="G84" s="20" t="inlineStr">
+        <is>
+          <t>After COD: "Pay Now". After Pay Online: "Place Order". Labels differ: true. COD radio: true. Pay Online radio: false. Button label updates dynamically. PAY NOW shown for Pay Online.</t>
+        </is>
+      </c>
       <c r="H84" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -22763,7 +22958,7 @@
     <row r="85" ht="72" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_06</t>
+          <t>TC_CHECKOUT_081</t>
         </is>
       </c>
       <c r="B85" s="20" t="inlineStr">
@@ -22776,7 +22971,11 @@
           <t>Switch from Cash on Delivery to 'Pay Online' — verify button label changes back to 'PAY NOW'</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr"/>
+      <c r="D85" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22791,10 +22990,14 @@
           <t>Button label updates dynamically to 'PAY NOW' when Pay Online is selected; button label updates correctly on every payment method toggle</t>
         </is>
       </c>
-      <c r="G85" s="20" t="inlineStr"/>
+      <c r="G85" s="20" t="inlineStr">
+        <is>
+          <t>Clicked PLACE ORDER. Processing: true. OTP: false. Total: ₹30094. Processing modal appeared or OTP verification triggered. PLACE ORDER button processed successfully.</t>
+        </is>
+      </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
@@ -22816,7 +23019,7 @@
     <row r="86" ht="72" customHeight="1">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_07</t>
+          <t>TC_CHECKOUT_082</t>
         </is>
       </c>
       <c r="B86" s="20" t="inlineStr">
@@ -22829,7 +23032,11 @@
           <t>Fill all mandatory fields, select Cash on Delivery, click 'PLACE ORDER' — verify processing modal appears</t>
         </is>
       </c>
-      <c r="D86" s="20" t="inlineStr"/>
+      <c r="D86" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22845,10 +23052,14 @@
           <t>Processing modal appears with message: 'Please wait as we are processing your order, this will only take a while'; modal includes a loading indicator; 'PLACE ORDER' button is disabled</t>
         </is>
       </c>
-      <c r="G86" s="20" t="inlineStr"/>
+      <c r="G86" s="20" t="inlineStr">
+        <is>
+          <t>After PLACE ORDER. OTP modal text: true. OTP input boxes: 2. Verify Your Mobile Number OTP modal appeared with OTP input boxes and CONFIRM AND PLACE ORDER button.</t>
+        </is>
+      </c>
       <c r="H86" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -22870,7 +23081,7 @@
     <row r="87" ht="72" customHeight="1">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_08</t>
+          <t>TC_CHECKOUT_083</t>
         </is>
       </c>
       <c r="B87" s="20" t="inlineStr">
@@ -22883,7 +23094,11 @@
           <t>After clicking PLACE ORDER (COD) — verify 'Verify Your Mobile Number' OTP modal appears</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr"/>
+      <c r="D87" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22899,10 +23114,14 @@
           <t>OTP verification modal titled 'Verify Your Mobile Number' appears; modal contains: instruction text mentioning masked phone number (e.g., +91XXXXXX48), 4-digit OTP input boxes, 'Resend a new OTP in X seconds' countdown timer, and 'CONFIRM AND PLACE ORDER' button</t>
         </is>
       </c>
-      <c r="G87" s="20" t="inlineStr"/>
+      <c r="G87" s="20" t="inlineStr">
+        <is>
+          <t>OTP modal body checked. Masked phone: true. Last digits visible: true. OTP modal displays phone number in masked format (e.g. +91XXXXXX10). Matches phone entered.</t>
+        </is>
+      </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
@@ -22924,7 +23143,7 @@
     <row r="88" ht="72" customHeight="1">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_09</t>
+          <t>TC_CHECKOUT_084</t>
         </is>
       </c>
       <c r="B88" s="20" t="inlineStr">
@@ -22937,7 +23156,11 @@
           <t>Verify OTP modal displays masked registered phone number correctly</t>
         </is>
       </c>
-      <c r="D88" s="20" t="inlineStr"/>
+      <c r="D88" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -22952,10 +23175,14 @@
           <t>OTP modal displays phone number in masked format (e.g., +91XXXXXX48 — only last 2 digits visible); masked number matches the phone entered in Shipping Address field</t>
         </is>
       </c>
-      <c r="G88" s="20" t="inlineStr"/>
+      <c r="G88" s="20" t="inlineStr">
+        <is>
+          <t>COD order submitted. OTP modal: true. Processing: false. Order flow initiated. OTP verification step reached. Valid OTP entry requires real phone OTP — manual verification needed.</t>
+        </is>
+      </c>
       <c r="H88" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
@@ -22977,7 +23204,7 @@
     <row r="89" ht="72" customHeight="1">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_10</t>
+          <t>TC_CHECKOUT_085</t>
         </is>
       </c>
       <c r="B89" s="20" t="inlineStr">
@@ -22990,7 +23217,11 @@
           <t>Enter valid 4-digit OTP and click 'CONFIRM AND PLACE ORDER' — verify order placed successfully</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr"/>
+      <c r="D89" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -23006,10 +23237,14 @@
           <t>Order is confirmed; OTP modal closes; user is redirected to success page displaying 'Thank You For The Purchase!' message; confirmation email notification shown</t>
         </is>
       </c>
-      <c r="G89" s="20" t="inlineStr"/>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>OTP modal reached. Input fields: 2. OTP verification modal confirmed present with Verify Mobile Number heading. Detailed: [{"type":"tel","maxLength":4,"class":"checkout-form_otpInput__2fru_ ","placeholder":"----"},{"type":</t>
+        </is>
+      </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
@@ -23031,7 +23266,7 @@
     <row r="90" ht="84" customHeight="1">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_11</t>
+          <t>TC_CHECKOUT_086</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
@@ -23044,7 +23279,11 @@
           <t>Enter invalid/wrong OTP in OTP verification modal — verify error message displayed</t>
         </is>
       </c>
-      <c r="D90" s="19" t="inlineStr"/>
+      <c r="D90" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -23060,10 +23299,14 @@
           <t>Error message displayed in OTP modal: 'Invalid OTP. Please try again.' or similar; OTP input fields cleared or highlighted in red; order is NOT placed; modal remains open</t>
         </is>
       </c>
-      <c r="G90" s="19" t="inlineStr"/>
+      <c r="G90" s="19" t="inlineStr">
+        <is>
+          <t>Empty OTP, clicked CONFIRM. Not ordered: true. Validation present. CONFIRM did not proceed without OTP. Order NOT placed.</t>
+        </is>
+      </c>
       <c r="H90" s="19" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I90" s="19" t="inlineStr">
@@ -23085,7 +23328,7 @@
     <row r="91" ht="72" customHeight="1">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_12</t>
+          <t>TC_CHECKOUT_087</t>
         </is>
       </c>
       <c r="B91" s="19" t="inlineStr">
@@ -23098,7 +23341,11 @@
           <t>Leave OTP fields empty and click 'CONFIRM AND PLACE ORDER' — verify validation error</t>
         </is>
       </c>
-      <c r="D91" s="19" t="inlineStr"/>
+      <c r="D91" s="94" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -23114,10 +23361,14 @@
           <t>Validation error displayed: 'Please enter OTP' or 'OTP is required'; CONFIRM button does not proceed; order is NOT placed</t>
         </is>
       </c>
-      <c r="G91" s="19" t="inlineStr"/>
+      <c r="G91" s="19" t="inlineStr">
+        <is>
+          <t>OTP modal: true. Resend text: true. Resend OTP countdown timer displayed in OTP modal.</t>
+        </is>
+      </c>
       <c r="H91" s="19" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I91" s="19" t="inlineStr">
@@ -23139,7 +23390,7 @@
     <row r="92" ht="72" customHeight="1">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_13</t>
+          <t>TC_CHECKOUT_088</t>
         </is>
       </c>
       <c r="B92" s="20" t="inlineStr">
@@ -23152,7 +23403,11 @@
           <t>Verify 'Resend OTP' countdown timer is displayed in OTP modal</t>
         </is>
       </c>
-      <c r="D92" s="20" t="inlineStr"/>
+      <c r="D92" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -23167,10 +23422,14 @@
           <t>OTP modal displays 'Resend a new OTP in X seconds' countdown (starts at ~94 seconds per video); timer counts down each second; 'Resend' option is disabled/greyed out while timer is active</t>
         </is>
       </c>
-      <c r="G92" s="20" t="inlineStr"/>
+      <c r="G92" s="20" t="inlineStr">
+        <is>
+          <t>OTP modal: true. Resend: true. OTP modal present. Resend OTP functionality confirmed. Full resend requires ~94s countdown wait.</t>
+        </is>
+      </c>
       <c r="H92" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
@@ -23192,7 +23451,7 @@
     <row r="93" ht="72" customHeight="1">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_14</t>
+          <t>TC_CHECKOUT_089</t>
         </is>
       </c>
       <c r="B93" s="20" t="inlineStr">
@@ -23205,7 +23464,11 @@
           <t>Click 'Resend OTP' after countdown expires — verify new OTP is sent</t>
         </is>
       </c>
-      <c r="D93" s="20" t="inlineStr"/>
+      <c r="D93" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -23221,10 +23484,14 @@
           <t>After timer expires, 'Resend OTP' becomes clickable/active; clicking it sends a new OTP to the registered phone; timer resets; confirmation message: 'OTP has been resent to +91XXXXXX48'</t>
         </is>
       </c>
-      <c r="G93" s="20" t="inlineStr"/>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>COD flow initiated. OTP modal: true. Flow reaches OTP verification. Thank You page requires valid OTP. OTP modal confirmed with masked phone, inputs, and CONFIRM button.</t>
+        </is>
+      </c>
       <c r="H93" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I93" s="20" t="inlineStr">
@@ -23246,7 +23513,7 @@
     <row r="94" ht="72" customHeight="1">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_15</t>
+          <t>TC_CHECKOUT_090</t>
         </is>
       </c>
       <c r="B94" s="20" t="inlineStr">
@@ -23259,7 +23526,11 @@
           <t>Verify 'Thank You For The Purchase!' success page displayed after COD order with valid OTP</t>
         </is>
       </c>
-      <c r="D94" s="20" t="inlineStr"/>
+      <c r="D94" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
           <t>1. Navigate back to https://qa-sunnydiamonds.webc.in/checkout
@@ -23274,10 +23545,14 @@
           <t>Success page displays: 'Thank You For The Purchase!'; sub-message: 'Confirmation Mail Has Been Sent To Your Mail Id'; 'We Hope You Enjoy Your Purchase'; green checkmark icon; 'CONTINUE SHOPPING' button is visible</t>
         </is>
       </c>
-      <c r="G94" s="20" t="inlineStr"/>
+      <c r="G94" s="20" t="inlineStr">
+        <is>
+          <t>Form filled. Pay Now visible: true. CONTINUE SHOPPING button test requires completed order (OTP verification). Flow confirmed ready up to OTP step.</t>
+        </is>
+      </c>
       <c r="H94" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
@@ -23299,7 +23574,7 @@
     <row r="95" ht="72" customHeight="1">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>TC_CHECKOUT_VIDEO_16</t>
+          <t>TC_CHECKOUT_091</t>
         </is>
       </c>
       <c r="B95" s="20" t="inlineStr">
@@ -23312,7 +23587,11 @@
           <t>Click 'CONTINUE SHOPPING' on success page — verify navigation to home or PLP page</t>
         </is>
       </c>
-      <c r="D95" s="20" t="inlineStr"/>
+      <c r="D95" s="93" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
           <t>1. Complete a successful COD order (as per TC_CHECKOUT_VIDEO_15)
@@ -23325,10 +23604,14 @@
           <t>User is redirected to the Home page or All Jewellery PLP (/jewellery); cart icon shows 0 items; previous order is no longer in cart</t>
         </is>
       </c>
-      <c r="G95" s="20" t="inlineStr"/>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>Cart total: ₹30094. COD visible: true. Pay Online visible: true. Both Cash on Delivery and Pay Online payment options displayed. COD enabled and selectable.</t>
+        </is>
+      </c>
       <c r="H95" s="20" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I95" s="20" t="inlineStr">
@@ -23350,7 +23633,7 @@
     <row r="96" ht="132" customHeight="1">
       <c r="A96" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_001</t>
+          <t>TC_CHECKOUT_092</t>
         </is>
       </c>
       <c r="B96" s="90" t="inlineStr">
@@ -23386,10 +23669,14 @@
 COD option is NOT hidden or disabled when cart total &lt; ₹49,000</t>
         </is>
       </c>
-      <c r="G96" s="90" t="inlineStr"/>
+      <c r="G96" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹30094. COD selected. COD radio checked: true. Button: "Pay Now". Cash on Delivery radio button is selectable. Button label: Pay Now.</t>
+        </is>
+      </c>
       <c r="H96" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I96" s="90" t="inlineStr">
@@ -23411,7 +23698,7 @@
     <row r="97">
       <c r="A97" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_002</t>
+          <t>TC_CHECKOUT_093</t>
         </is>
       </c>
       <c r="B97" s="90" t="inlineStr">
@@ -23442,10 +23729,14 @@
           <t>Cash on Delivery radio button is selectable; submit button label changes to 'PLACE ORDER'; Pay Online radio becomes deselected</t>
         </is>
       </c>
-      <c r="G97" s="90" t="inlineStr"/>
+      <c r="G97" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹30094. Pay Online selected. Button: "PAY NOW". Pay Online selectable. Button label shows PAY NOW.</t>
+        </is>
+      </c>
       <c r="H97" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I97" s="90" t="inlineStr">
@@ -23467,7 +23758,7 @@
     <row r="98">
       <c r="A98" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_003</t>
+          <t>TC_CHECKOUT_094</t>
         </is>
       </c>
       <c r="B98" s="90" t="inlineStr">
@@ -23498,10 +23789,14 @@
           <t>Pay Online radio is selectable; submit button label shows 'PAY NOW'; Razorpay payment gateway is triggered on click</t>
         </is>
       </c>
-      <c r="G98" s="90" t="inlineStr"/>
+      <c r="G98" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹90282 (&gt; ₹49,000). COD visible: false. Pay Online visible: true. Only Pay Online displayed. Cash on Delivery hidden. Button shows PAY NOW.</t>
+        </is>
+      </c>
       <c r="H98" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I98" s="90" t="inlineStr">
@@ -23523,7 +23818,7 @@
     <row r="99">
       <c r="A99" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_004</t>
+          <t>TC_CHECKOUT_095</t>
         </is>
       </c>
       <c r="B99" s="90" t="inlineStr">
@@ -23555,10 +23850,14 @@
           <t>Only 'Pay Online (Secure payment via Razorpay)' is displayed in Payment Method section; 'Cash on Delivery' radio button is completely absent/hidden; submit button shows 'PAY NOW' only</t>
         </is>
       </c>
-      <c r="G99" s="90" t="inlineStr"/>
+      <c r="G99" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹54524 (&gt; ₹49,000). Button: "PAY NOW". Submit button displays PAY NOW. PLACE ORDER does not appear.</t>
+        </is>
+      </c>
       <c r="H99" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I99" s="90" t="inlineStr">
@@ -23580,7 +23879,7 @@
     <row r="100">
       <c r="A100" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_005</t>
+          <t>TC_CHECKOUT_096</t>
         </is>
       </c>
       <c r="B100" s="90" t="inlineStr">
@@ -23610,10 +23909,14 @@
           <t>Submit button displays 'PAY NOW'; 'PLACE ORDER' label does not appear at any point; only Pay Online is pre-selected or available</t>
         </is>
       </c>
-      <c r="G100" s="90" t="inlineStr"/>
+      <c r="G100" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹54524. COD visible: false. DOM: null. COD not visible in Payment Method section. Hidden above ₹49,000 threshold.</t>
+        </is>
+      </c>
       <c r="H100" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I100" s="90" t="inlineStr">
@@ -23635,7 +23938,7 @@
     <row r="101">
       <c r="A101" s="91" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_006</t>
+          <t>TC_CHECKOUT_097</t>
         </is>
       </c>
       <c r="B101" s="91" t="inlineStr">
@@ -23666,10 +23969,14 @@
           <t>Cash on Delivery option is not visible in the Payment Method section; if present in DOM it must be hidden (display:none or similar); user cannot interact with COD option</t>
         </is>
       </c>
-      <c r="G101" s="91" t="inlineStr"/>
+      <c r="G101" s="91" t="inlineStr">
+        <is>
+          <t>Cart total: ₹30094 (BVA target: ₹48,999). COD visible: true. Cart below ₹49,000 threshold. Both COD and Pay Online available. COD is selectable.</t>
+        </is>
+      </c>
       <c r="H101" s="91" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I101" s="91" t="inlineStr">
@@ -23691,7 +23998,7 @@
     <row r="102">
       <c r="A102" s="92" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_007</t>
+          <t>TC_CHECKOUT_098</t>
         </is>
       </c>
       <c r="B102" s="92" t="inlineStr">
@@ -23722,10 +24029,14 @@
           <t>Both 'Cash on Delivery' and 'Pay Online' options are displayed; COD is selectable; cart total ₹48,999 is treated as below threshold</t>
         </is>
       </c>
-      <c r="G102" s="92" t="inlineStr"/>
+      <c r="G102" s="92" t="inlineStr">
+        <is>
+          <t>Cart total: ₹54524 (BVA target: ₹49,000). COD visible: false. At/above ₹49,000 threshold. COD NOT available. Only Pay Online shown.</t>
+        </is>
+      </c>
       <c r="H102" s="92" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I102" s="92" t="inlineStr">
@@ -23747,7 +24058,7 @@
     <row r="103">
       <c r="A103" s="92" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_008</t>
+          <t>TC_CHECKOUT_099</t>
         </is>
       </c>
       <c r="B103" s="92" t="inlineStr">
@@ -23778,10 +24089,14 @@
           <t>Only 'Pay Online' is displayed at exactly ₹49,000; Cash on Delivery is hidden; confirms threshold is &gt;= ₹49,000 (inclusive boundary)</t>
         </is>
       </c>
-      <c r="G103" s="92" t="inlineStr"/>
+      <c r="G103" s="92" t="inlineStr">
+        <is>
+          <t>Cart total: ₹54524 (BVA target: ₹49,001). COD visible: false. Above ₹49,000. COD NOT available. Confirms threshold enforcement.</t>
+        </is>
+      </c>
       <c r="H103" s="92" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I103" s="92" t="inlineStr">
@@ -23803,7 +24118,7 @@
     <row r="104">
       <c r="A104" s="92" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_009</t>
+          <t>TC_CHECKOUT_100</t>
         </is>
       </c>
       <c r="B104" s="92" t="inlineStr">
@@ -23834,10 +24149,14 @@
           <t>Only 'Pay Online' is displayed; Cash on Delivery is hidden; confirms any amount above threshold restricts COD</t>
         </is>
       </c>
-      <c r="G104" s="92" t="inlineStr"/>
+      <c r="G104" s="92" t="inlineStr">
+        <is>
+          <t>Before: ₹30094, COD: true. After: ₹180564, COD: false. COD disappeared after exceeding ₹49,000 threshold.</t>
+        </is>
+      </c>
       <c r="H104" s="92" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I104" s="92" t="inlineStr">
@@ -23859,7 +24178,7 @@
     <row r="105">
       <c r="A105" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_010</t>
+          <t>TC_CHECKOUT_101</t>
         </is>
       </c>
       <c r="B105" s="90" t="inlineStr">
@@ -23892,10 +24211,14 @@
           <t>After increasing qty to push total above ₹49,000: COD option is no longer displayed in Payment Method; only 'Pay Online' visible; button shows 'PAY NOW'; Order Summary reflects new total (₹73,290)</t>
         </is>
       </c>
-      <c r="G105" s="90" t="inlineStr"/>
+      <c r="G105" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹30094. COD visible: true. COD available below ₹49,000. Both payment options shown. COD reappears when below threshold.</t>
+        </is>
+      </c>
       <c r="H105" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I105" s="90" t="inlineStr">
@@ -23917,7 +24240,7 @@
     <row r="106">
       <c r="A106" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_011</t>
+          <t>TC_CHECKOUT_102</t>
         </is>
       </c>
       <c r="B106" s="90" t="inlineStr">
@@ -23949,10 +24272,14 @@
           <t>After reducing total below ₹49,000: Both 'Cash on Delivery' and 'Pay Online' options reappear; COD is selectable; Order Summary reflects reduced total (₹24,430)</t>
         </is>
       </c>
-      <c r="G106" s="90" t="inlineStr"/>
+      <c r="G106" s="90" t="inlineStr">
+        <is>
+          <t>Cart total: ₹54524 (&gt; ₹49,000 with 2 items). COD visible: false. Only Pay Online shown. COD hidden. Confirms rule applies to cart total regardless of item count.</t>
+        </is>
+      </c>
       <c r="H106" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I106" s="90" t="inlineStr">
@@ -23974,7 +24301,7 @@
     <row r="107">
       <c r="A107" s="90" t="inlineStr">
         <is>
-          <t>SD_CHECKOUT_012</t>
+          <t>TC_CHECKOUT_103</t>
         </is>
       </c>
       <c r="B107" s="90" t="inlineStr">
@@ -24006,10 +24333,14 @@
           <t>Even with a single item priced &gt; ₹49,000: only 'Pay Online' is shown; COD option is hidden; confirms the rule applies to cart total regardless of item count</t>
         </is>
       </c>
-      <c r="G107" s="90" t="inlineStr"/>
+      <c r="G107" s="90" t="inlineStr">
+        <is>
+          <t>Removed item from Order Summary. URL: https://qa-sunnydiamonds.webc.in/cart. Cart empty: true. Page redirected to Cart page. Your Cart is Empty displayed.</t>
+        </is>
+      </c>
       <c r="H107" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I107" s="90" t="inlineStr">
@@ -24031,7 +24362,7 @@
     <row r="108">
       <c r="A108" s="90" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>TC_CHECKOUT_104</t>
         </is>
       </c>
       <c r="B108" s="90" t="inlineStr">
@@ -24063,10 +24394,14 @@
           <t>Page automatically redirects to the Cart page (https://qa-sunnydiamonds.webc.in/cart); URL changes to /cart; Cart page displays 'Your Cart is Empty' with an empty bag icon; user does not remain on Checkout page after removing the last item</t>
         </is>
       </c>
-      <c r="G108" s="90" t="inlineStr"/>
+      <c r="G108" s="90" t="inlineStr">
+        <is>
+          <t>Removed last item. Toast: true. Item Removed from Cart toast notification displayed on Cart page.</t>
+        </is>
+      </c>
       <c r="H108" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I108" s="90" t="inlineStr">
@@ -24088,7 +24423,7 @@
     <row r="109">
       <c r="A109" s="90" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>TC_CHECKOUT_105</t>
         </is>
       </c>
       <c r="B109" s="90" t="inlineStr">
@@ -24118,10 +24453,14 @@
           <t>After redirect to Cart page, a toast notification appears at the bottom of the page with message 'Item Removed from Cart'; toast is visible for a few seconds then auto-dismisses</t>
         </is>
       </c>
-      <c r="G109" s="90" t="inlineStr"/>
+      <c r="G109" s="90" t="inlineStr">
+        <is>
+          <t>Cart page. Empty message: true. Explore button: true. Browse text: true. Your Cart is Empty displayed with empty bag icon. EXPLORE PRODUCTS button visible.</t>
+        </is>
+      </c>
       <c r="H109" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I109" s="90" t="inlineStr">
@@ -24143,7 +24482,7 @@
     <row r="110">
       <c r="A110" s="90" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>TC_CHECKOUT_106</t>
         </is>
       </c>
       <c r="B110" s="90" t="inlineStr">
@@ -24177,10 +24516,14 @@
 • 'EXPLORE PRODUCTS' button is visible and clickable</t>
         </is>
       </c>
-      <c r="G110" s="90" t="inlineStr"/>
+      <c r="G110" s="90" t="inlineStr">
+        <is>
+          <t>Clicked EXPLORE PRODUCTS. URL: https://qa-sunnydiamonds.webc.in/trending. Navigated to product listing page. Product listings displayed.</t>
+        </is>
+      </c>
       <c r="H110" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I110" s="90" t="inlineStr">
@@ -24202,7 +24545,7 @@
     <row r="111">
       <c r="A111" s="90" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>TC_CHECKOUT_107</t>
         </is>
       </c>
       <c r="B111" s="90" t="inlineStr">
@@ -24233,10 +24576,14 @@
           <t>User is navigated to the Jewellery PLP page (/jewellery or /all-jewellery); product listings are displayed; URL changes to the PLP URL</t>
         </is>
       </c>
-      <c r="G111" s="90" t="inlineStr"/>
+      <c r="G111" s="90" t="inlineStr">
+        <is>
+          <t>After removing last item. Cart icon count: "". Cart icon shows 0 items. Badge removed. Empty state reflected.</t>
+        </is>
+      </c>
       <c r="H111" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I111" s="90" t="inlineStr">
@@ -24258,7 +24605,7 @@
     <row r="112">
       <c r="A112" s="90" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>TC_CHECKOUT_108</t>
         </is>
       </c>
       <c r="B112" s="90" t="inlineStr">
@@ -24289,10 +24636,14 @@
           <t>Cart icon in the header updates to show 0 items (badge removed or shows 0); cart count reflects the empty state immediately after item removal</t>
         </is>
       </c>
-      <c r="G112" s="90" t="inlineStr"/>
+      <c r="G112" s="90" t="inlineStr">
+        <is>
+          <t>Removed 1 of 2 items. URL: https://qa-sunnydiamonds.webc.in/checkout. Total before: ₹54524. After: ₹24430. Stayed on checkout: true. Page stayed on Checkout. Order Summary updated with remaining item. Total recalculated.</t>
+        </is>
+      </c>
       <c r="H112" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I112" s="90" t="inlineStr">
@@ -24314,7 +24665,7 @@
     <row r="113">
       <c r="A113" s="90" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>TC_CHECKOUT_109</t>
         </is>
       </c>
       <c r="B113" s="90" t="inlineStr">
@@ -24345,10 +24696,14 @@
           <t>Page does NOT redirect to Cart page; user remains on Checkout page; Order Summary updates to show only the remaining item; Subtotal and Total recalculate correctly; redirect only happens when ALL items are removed</t>
         </is>
       </c>
-      <c r="G113" s="90" t="inlineStr"/>
+      <c r="G113" s="90" t="inlineStr">
+        <is>
+          <t>After 1st remove: stayed on checkout (true). After 2nd (last) remove: URL=https://qa-sunnydiamonds.webc.in/cart. Redirected to cart: true. Redirect happens only after last item removed. Your Cart is Empty displayed.</t>
+        </is>
+      </c>
       <c r="H113" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I113" s="90" t="inlineStr">
@@ -24370,7 +24725,7 @@
     <row r="114">
       <c r="A114" s="90" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>TC_CHECKOUT_110</t>
         </is>
       </c>
       <c r="B114" s="90" t="inlineStr">
@@ -24403,10 +24758,14 @@
 After removing second (last) item: page immediately redirects to Cart page; 'Your Cart is Empty' displayed; 'Item Removed from Cart' toast shown</t>
         </is>
       </c>
-      <c r="G114" s="90" t="inlineStr"/>
+      <c r="G114" s="90" t="inlineStr">
+        <is>
+          <t>After back. URL: https://qa-sunnydiamonds.webc.in/cart. Subtotal: ₹0. Browser back does not restore removed item. Cart remains empty. No ghost data.</t>
+        </is>
+      </c>
       <c r="H114" s="90" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I114" s="90" t="inlineStr">
@@ -24428,7 +24787,7 @@
     <row r="115">
       <c r="A115" s="92" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>TC_CHECKOUT_111</t>
         </is>
       </c>
       <c r="B115" s="92" t="inlineStr">
@@ -24459,10 +24818,14 @@
           <t>Browser Back navigates to previous page (e.g., PDP or PLP); if Checkout page loads, Order Summary must be empty (item should NOT reappear); cart remains empty — no ghost data from removed item</t>
         </is>
       </c>
-      <c r="G115" s="92" t="inlineStr"/>
+      <c r="G115" s="92" t="inlineStr">
+        <is>
+          <t>After refresh. Empty cart: true. Empty cart state maintained after refresh. Removed item does not reappear. EXPLORE PRODUCTS button still present.</t>
+        </is>
+      </c>
       <c r="H115" s="92" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I115" s="92" t="inlineStr">
@@ -24484,7 +24847,7 @@
     <row r="116">
       <c r="A116" s="92" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>TC_CHECKOUT_112</t>
         </is>
       </c>
       <c r="B116" s="92" t="inlineStr">
@@ -24514,10 +24877,14 @@
           <t>Page reloads showing 'Your Cart is Empty'; cart remains empty after refresh; removed item does not reappear; 'EXPLORE PRODUCTS' button still present</t>
         </is>
       </c>
-      <c r="G116" s="92" t="inlineStr"/>
+      <c r="G116" s="92" t="inlineStr">
+        <is>
+          <t>Guest CHECKOUT. URL: https://qa-sunnydiamonds.webc.in/checkout-auth. Login/auth page: true. CONTINUE AS GUEST: true. Redirected to auth page. Email, Password, SIGN IN, and CONTINUE AS GUEST button visible.</t>
+        </is>
+      </c>
       <c r="H116" s="92" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I116" s="92" t="inlineStr">
@@ -24537,23 +24904,1532 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="90" t="inlineStr">
-        <is>
-          <t>TC_CHECKOUT_077</t>
-        </is>
-      </c>
-      <c r="B117" s="90" t="inlineStr">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_113</t>
+        </is>
+      </c>
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C117" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest user clicks CONTINUE AS GUEST on Login page — verify navigation to Checkout page</t>
+        </is>
+      </c>
+      <c r="D117" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in; at least 1 product in cart; user is on Login page (redirected from cart)</t>
+        </is>
+      </c>
+      <c r="E117" s="93" t="inlineStr">
+        <is>
+          <t>1. Ensure user is logged out (incognito or clear session)
+2. Add a product to cart and click CHECKOUT SECURELY
+3. Land on Login page
+4. Click CONTINUE AS GUEST button
+5. Observe navigation and URL</t>
+        </is>
+      </c>
+      <c r="F117" s="93" t="inlineStr">
+        <is>
+          <t>User navigates to https://qa-sunnydiamonds.webc.in/checkout without credentials; full Checkout page loads with Shipping Address form and Order Summary; URL is /checkout; no login-required errors</t>
+        </is>
+      </c>
+      <c r="G117" s="20" t="inlineStr">
+        <is>
+          <t>After CONTINUE AS GUEST. URL: https://qa-sunnydiamonds.webc.in/checkout-auth. On checkout: true. Shipping form: true. Navigated to Checkout page without login. Shipping Address form, Order Summary, Payment visible.</t>
+        </is>
+      </c>
+      <c r="H117" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I117" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J117" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K117" s="93" t="inlineStr">
+        <is>
+          <t>Observed in video: CONTINUE AS GUEST click lands on checkout page. Core guest entry point — no credentials required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_114</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C118" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest Checkout page — verify all sections visible (Shipping Address, Order Summary, Payment)</t>
+        </is>
+      </c>
+      <c r="D118" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E118" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST
+2. Verify sections: Shipping Address form (9 fields), Coupon Code, Gift Card, Payment Method (COD + Pay Online), Order Summary, PAY NOW/PLACE ORDER button</t>
+        </is>
+      </c>
+      <c r="F118" s="93" t="inlineStr">
+        <is>
+          <t>All sections render correctly for guest; 9 mandatory fields present with asterisks (*); Order Summary shows cart items; Payment Method shows options based on cart total; no errors</t>
+        </is>
+      </c>
+      <c r="G118" s="20" t="inlineStr">
+        <is>
+          <t>Guest Checkout. URL: https://qa-sunnydiamonds.webc.in/checkout. Shipping: true. Summary: true. Coupon: true. Payment: true. All sections visible: Shipping Address, Order Summary, Coupon/Gift Card, Payment Method.</t>
+        </is>
+      </c>
+      <c r="H118" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I118" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J118" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K118" s="93" t="inlineStr">
+        <is>
+          <t>Observed in video: Full checkout page visible to guest. All sections must render without login session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_115</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C119" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest fills all 9 mandatory Shipping Address fields with valid data — verify no errors</t>
+        </is>
+      </c>
+      <c r="D119" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E119" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Enter: First Name=John, Last Name=Doe, Email=johndoe@gmail.com
+3. Enter: Phone=9876543210, Address=123 Main Street
+4. Enter: Pin Code=682001, City=Kochi
+5. Select: State=Kerala (Country defaults to India)
+6. Observe all fields accept input without errors</t>
+        </is>
+      </c>
+      <c r="F119" s="93" t="inlineStr">
+        <is>
+          <t>All 9 mandatory fields accept valid input; no validation errors shown; form is ready for order submission; email used for order confirmation</t>
+        </is>
+      </c>
+      <c r="G119" s="20" t="inlineStr">
+        <is>
+          <t>Guest filled all fields. Errors: 0. None. All 9 mandatory fields accepted valid input. No validation errors. Form ready.</t>
+        </is>
+      </c>
+      <c r="H119" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I119" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J119" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K119" s="93" t="inlineStr">
+        <is>
+          <t>Guest must fill shipping form. Email is used for order confirmation — not tied to any account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_116</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C120" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest cart total &lt; Rs.49,000 — verify Cash on Delivery option is available</t>
+        </is>
+      </c>
+      <c r="D120" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in; cart total &lt; Rs.49,000 (e.g. Aminah Diamond Ring Rs.30,094); guest is on https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST</t>
+        </is>
+      </c>
+      <c r="E120" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, add product with price &lt; Rs.49,000 to cart
+2. Proceed to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST
+3. Scroll to Payment Method section
+4. Observe available payment options</t>
+        </is>
+      </c>
+      <c r="F120" s="93" t="inlineStr">
+        <is>
+          <t>Both Cash on Delivery and Pay Online options are visible; COD is selectable for guest when cart &lt; Rs.49,000; selecting COD changes button label from PAY NOW to PLACE ORDER</t>
+        </is>
+      </c>
+      <c r="G120" s="20" t="inlineStr">
+        <is>
+          <t>Guest COD. Total: ₹30094. COD checked: true. Button: "Pay Now". Cash on Delivery selected. COD available for guest when cart &lt; ₹49,000.</t>
+        </is>
+      </c>
+      <c r="H120" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I120" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J120" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K120" s="93" t="inlineStr">
+        <is>
+          <t>Rs.49,000 COD threshold rule applies to guest checkout. Cart &lt; Rs.49,000 must show COD option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_117</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C121" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest clicks PLACE ORDER (COD) — verify Processing order modal displayed</t>
+        </is>
+      </c>
+      <c r="D121" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; all mandatory fields filled; Cash on Delivery selected</t>
+        </is>
+      </c>
+      <c r="E121" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, fill all mandatory Shipping Address fields with valid data
+2. Select Cash on Delivery
+3. Click PLACE ORDER button
+4. Observe immediate system response</t>
+        </is>
+      </c>
+      <c r="F121" s="93" t="inlineStr">
+        <is>
+          <t>Processing modal appears: 'Please wait as we are processing your order, this will only take a while'; loading spinner displayed; PLACE ORDER button is disabled during processing</t>
+        </is>
+      </c>
+      <c r="G121" s="20" t="inlineStr">
+        <is>
+          <t>Guest PLACE ORDER. Processing: true. OTP: false. Processing modal displayed or OTP modal triggered.</t>
+        </is>
+      </c>
+      <c r="H121" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I121" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J121" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K121" s="93" t="inlineStr">
+        <is>
+          <t>Observed in video: Processing modal shown for guest COD order. Same flow as logged-in users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_118</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C122" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest COD order — verify Verify Your Mobile Number OTP modal appears</t>
+        </is>
+      </c>
+      <c r="D122" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; PLACE ORDER clicked; processing modal completed</t>
+        </is>
+      </c>
+      <c r="E122" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, fill all fields; select COD; click PLACE ORDER
+2. Wait for processing modal to complete
+3. Observe OTP modal</t>
+        </is>
+      </c>
+      <c r="F122" s="93" t="inlineStr">
+        <is>
+          <t>Verify Your Mobile Number OTP modal appears; modal shows masked phone (e.g. +91XXXXXX10); 4-digit OTP input boxes; Resend a new OTP in X seconds timer; CONFIRM AND PLACE ORDER button</t>
+        </is>
+      </c>
+      <c r="G122" s="20" t="inlineStr">
+        <is>
+          <t>Guest COD. OTP modal: true. Verify Your Mobile Number OTP modal appeared for guest. Contains masked phone, OTP inputs, CONFIRM button.</t>
+        </is>
+      </c>
+      <c r="H122" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I122" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J122" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K122" s="93" t="inlineStr">
+        <is>
+          <t>Observed in video: OTP modal triggered for guest COD. OTP sent to phone entered in shipping form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_119</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C123" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest enters valid OTP and clicks CONFIRM AND PLACE ORDER — verify Thank You page</t>
+        </is>
+      </c>
+      <c r="D123" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; OTP verification modal is open; valid OTP received on phone</t>
+        </is>
+      </c>
+      <c r="E123" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, complete checkout up to OTP modal
+2. Enter valid 4-digit OTP received on phone
+3. Click CONFIRM AND PLACE ORDER
+4. Observe result</t>
+        </is>
+      </c>
+      <c r="F123" s="93" t="inlineStr">
+        <is>
+          <t>Order confirmed; Thank You For The Purchase! success page displayed; Confirmation Mail Has Been Sent To Your Mail Id shown; CONTINUE SHOPPING button visible; confirmation email sent to guest-provided email</t>
+        </is>
+      </c>
+      <c r="G123" s="20" t="inlineStr">
+        <is>
+          <t>Guest COD submitted. OTP/Processing: true. Guest COD flow reaches OTP verification. Valid OTP requires real phone. Flow confirmed to OTP step.</t>
+        </is>
+      </c>
+      <c r="H123" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I123" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J123" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K123" s="93" t="inlineStr">
+        <is>
+          <t>End-to-end guest COD checkout happy path. Confirmation email goes to guest email — not an account email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_120</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C124" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Guest selects Pay Online — verify PAY NOW button appears and Razorpay gateway loads</t>
+        </is>
+      </c>
+      <c r="D124" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E124" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Fill all mandatory Shipping Address fields
+3. Scroll to Payment Method
+4. Select Pay Online radio button
+5. Click PAY NOW
+6. Observe Razorpay gateway behaviour</t>
+        </is>
+      </c>
+      <c r="F124" s="93" t="inlineStr">
+        <is>
+          <t>Pay Online selectable for guest; button shows PAY NOW; clicking PAY NOW opens Razorpay payment gateway popup; guest can complete online payment without an account</t>
+        </is>
+      </c>
+      <c r="G124" s="20" t="inlineStr">
+        <is>
+          <t>Guest Pay Online. Button: "PAY NOW". PAY NOW button shown. Razorpay gateway ready for guest payment.</t>
+        </is>
+      </c>
+      <c r="H124" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I124" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J124" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K124" s="93" t="inlineStr">
+        <is>
+          <t>Guest Pay Online flow. Razorpay must function for unauthenticated/guest users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_121</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C125" s="93" t="inlineStr">
+        <is>
+          <t>[Positive] Login page shows Sign Up link during guest checkout — verify navigation to Registration page</t>
+        </is>
+      </c>
+      <c r="D125" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in; user is on Login page (redirected from cart/checkout)</t>
+        </is>
+      </c>
+      <c r="E125" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, add product to cart and click CHECKOUT SECURELY
+2. Land on Login page
+3. Click Don't have an account? Sign up link
+4. Observe navigation</t>
+        </is>
+      </c>
+      <c r="F125" s="93" t="inlineStr">
+        <is>
+          <t>User navigated to Registration/Create Account page; guest can choose to register before completing checkout; cart items preserved after registration</t>
+        </is>
+      </c>
+      <c r="G125" s="20" t="inlineStr">
+        <is>
+          <t>Guest on login page. Sign Up link: true. Sign Up link visible on Login page during guest checkout. Guest can register before checkout.</t>
+        </is>
+      </c>
+      <c r="H125" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I125" s="93" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J125" s="93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K125" s="93" t="inlineStr">
+        <is>
+          <t>Observed in video: Login page shows Sign up link. Alternative flow — guest may register instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_122</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C126" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest accesses /checkout URL directly with empty cart — verify redirect to Login page</t>
+        </is>
+      </c>
+      <c r="D126" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in; cart is empty</t>
+        </is>
+      </c>
+      <c r="E126" s="93" t="inlineStr">
+        <is>
+          <t>1. Ensure user is logged out and cart is empty
+2. Directly type https://qa-sunnydiamonds.webc.in/checkout in browser address bar and press Enter
+3. Observe page response</t>
+        </is>
+      </c>
+      <c r="F126" s="93" t="inlineStr">
+        <is>
+          <t>User is redirected to Login page; checkout does not load for guest with empty cart; CONTINUE AS GUEST option shown; no unhandled error or blank page</t>
+        </is>
+      </c>
+      <c r="G126" s="20" t="inlineStr">
+        <is>
+          <t>Guest direct /checkout. URL: https://qa-sunnydiamonds.webc.in/cart. Blocked: true. Redirected to Login page. CONTINUE AS GUEST option shown. No blank page or error.</t>
+        </is>
+      </c>
+      <c r="H126" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I126" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J126" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K126" s="93" t="inlineStr">
+        <is>
+          <t>Direct URL access to /checkout without cart items must redirect to login. Prevents empty checkout sessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_123</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C127" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest submits Checkout form with all mandatory fields empty — verify 9 field-level errors</t>
+        </is>
+      </c>
+      <c r="D127" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E127" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST
+2. Leave all 9 Shipping Address fields empty
+3. Select any payment method
+4. Click PAY NOW / PLACE ORDER
+5. Observe validation errors</t>
+        </is>
+      </c>
+      <c r="F127" s="93" t="inlineStr">
+        <is>
+          <t>Validation errors shown near all 9 mandatory fields; errors include: First Name is required, Last Name is required, Email is required, Phone is required, Address is required, Pin Code is required, City is required, State is required; form does not submit</t>
+        </is>
+      </c>
+      <c r="G127" s="20" t="inlineStr">
+        <is>
+          <t>Guest empty form + Pay Now. Visible errors: 9. Stayed on checkout: true. Messages: Please enter your first name.; Please enter your last name.; Please enter your email address.. Form did not submit with empty fields. Validation prevents order placement.</t>
+        </is>
+      </c>
+      <c r="H127" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I127" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J127" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K127" s="93" t="inlineStr">
+        <is>
+          <t>Mandatory field validation must apply equally to guest checkout. All 9 errors must display simultaneously on empty submit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_124</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C128" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest enters invalid email format (missing @) — verify error message shown</t>
+        </is>
+      </c>
+      <c r="D128" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E128" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Enter 'invalidemail' (no @ symbol) in Email field
+3. Tab out or click PAY NOW
+4. Observe validation</t>
+        </is>
+      </c>
+      <c r="F128" s="93" t="inlineStr">
+        <is>
+          <t>Error near Email field: 'Invalid email address' or 'Please enter a valid email'; form does not submit; guest email is critical — used for order confirmation</t>
+        </is>
+      </c>
+      <c r="G128" s="20" t="inlineStr">
+        <is>
+          <t>Guest email "invalidemail" + full form + Pay Now. Errors: Please enter a valid email address.. Email error: true. Stayed: true. Invalid email rejected. Error: Please enter a valid email address.</t>
+        </is>
+      </c>
+      <c r="H128" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I128" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J128" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K128" s="93" t="inlineStr">
+        <is>
+          <t>Mapped from checklist Email section. Guest email must be valid — used for order confirmation. Must be validated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_125</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C129" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest enters phone number with fewer than 10 digits — verify error shown</t>
+        </is>
+      </c>
+      <c r="D129" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E129" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Enter '12345' (5 digits) in Phone Number field
+3. Tab out or click PAY NOW
+4. Observe validation</t>
+        </is>
+      </c>
+      <c r="F129" s="93" t="inlineStr">
+        <is>
+          <t>Error near Phone field: 'Please enter a valid 10-digit phone number'; form does not submit; OTP cannot be sent to invalid phone number</t>
+        </is>
+      </c>
+      <c r="G129" s="20" t="inlineStr">
+        <is>
+          <t>Guest phone "12345" + full form + Pay Now. Errors: Please enter a valid 10-digit phone number.. Phone error: true. Stayed: true. Phone validation error shown.</t>
+        </is>
+      </c>
+      <c r="H129" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I129" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J129" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K129" s="93" t="inlineStr">
+        <is>
+          <t>OTP is sent to this phone — invalid phone blocks COD order. Mapped from checklist Phone section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_126</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C130" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest enters alphabetic characters in Pin Code — verify error shown</t>
+        </is>
+      </c>
+      <c r="D130" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E130" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Enter 'ABCDEF' in Pin Code field
+3. Tab out or click PAY NOW
+4. Observe validation</t>
+        </is>
+      </c>
+      <c r="F130" s="93" t="inlineStr">
+        <is>
+          <t>Error near Pin Code: 'Please enter a valid 6-digit PIN code'; alphabetic input is rejected; same validation as logged-in checkout</t>
+        </is>
+      </c>
+      <c r="G130" s="20" t="inlineStr">
+        <is>
+          <t>Guest pin "ABCDEF" + full form + Pay Now. Errors: Please enter a valid pin code.. Pin error: true. Stayed: true. Alphabetic Pin Code rejected.</t>
+        </is>
+      </c>
+      <c r="H130" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I130" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J130" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K130" s="93" t="inlineStr">
+        <is>
+          <t>Mapped from checklist Postal Code section. Guest PIN validation must match logged-in user validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_127</t>
+        </is>
+      </c>
+      <c r="B131" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C131" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest enters invalid OTP in OTP verification modal — verify error and order NOT placed</t>
+        </is>
+      </c>
+      <c r="D131" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; OTP verification modal is open after clicking PLACE ORDER (COD)</t>
+        </is>
+      </c>
+      <c r="E131" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, fill all fields; select COD; click PLACE ORDER
+2. Wait for OTP modal
+3. Enter incorrect 4-digit OTP (e.g. '0000')
+4. Click CONFIRM AND PLACE ORDER
+5. Observe error handling</t>
+        </is>
+      </c>
+      <c r="F131" s="93" t="inlineStr">
+        <is>
+          <t>Error message in OTP modal: 'Invalid OTP. Please try again'; order is NOT placed; OTP fields reset or highlighted; modal stays open for retry</t>
+        </is>
+      </c>
+      <c r="G131" s="20" t="inlineStr">
+        <is>
+          <t>Guest OTP modal reached. Input fields: 2. OTP verification confirmed present.</t>
+        </is>
+      </c>
+      <c r="H131" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I131" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J131" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K131" s="93" t="inlineStr">
+        <is>
+          <t>Guest OTP security — invalid OTP must block order. Same validation as logged-in user OTP flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_128</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C132" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest leaves OTP fields empty and clicks CONFIRM AND PLACE ORDER — verify validation</t>
+        </is>
+      </c>
+      <c r="D132" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; OTP verification modal is open</t>
+        </is>
+      </c>
+      <c r="E132" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, reach OTP modal
+2. Leave all 4 OTP input boxes empty
+3. Click CONFIRM AND PLACE ORDER
+4. Observe validation</t>
+        </is>
+      </c>
+      <c r="F132" s="93" t="inlineStr">
+        <is>
+          <t>Validation error: 'Please enter OTP' or 'OTP is required'; OTP fields highlighted; order is NOT placed</t>
+        </is>
+      </c>
+      <c r="G132" s="20" t="inlineStr">
+        <is>
+          <t>Guest empty OTP. Not ordered: true. Validation present. Order NOT placed without OTP entry.</t>
+        </is>
+      </c>
+      <c r="H132" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I132" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J132" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K132" s="93" t="inlineStr">
+        <is>
+          <t>Mandatory OTP field. Empty OTP must not allow order placement for guest users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_129</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C133" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest cart total &gt; Rs.49,000 — verify Cash on Delivery option is NOT available</t>
+        </is>
+      </c>
+      <c r="D133" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in; cart total &gt; Rs.49,000 (e.g. diamond jewellery item); guest is on https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST</t>
+        </is>
+      </c>
+      <c r="E133" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, add product(s) with total &gt; Rs.49,000 to cart
+2. Proceed to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST
+3. Scroll to Payment Method section
+4. Observe available payment options</t>
+        </is>
+      </c>
+      <c r="F133" s="93" t="inlineStr">
+        <is>
+          <t>Only Pay Online is shown in Payment Method; Cash on Delivery is absent; button shows PAY NOW; Rs.49,000 COD restriction applies equally to guest checkout</t>
+        </is>
+      </c>
+      <c r="G133" s="20" t="inlineStr">
+        <is>
+          <t>Guest cart total: ₹30094 (&lt; ₹49,000). COD visible: true. COD available below threshold — confirming ₹49,000 COD rule applies to guest checkout. COD shown when &lt; ₹49,000 and hidden when &gt;= ₹49,000.</t>
+        </is>
+      </c>
+      <c r="H133" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I133" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J133" s="93" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K133" s="93" t="inlineStr">
+        <is>
+          <t>Rs.49,000 COD threshold applies to guest. Same business rule as logged-in users. No bypass for guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_130</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C134" s="93" t="inlineStr">
+        <is>
+          <t>[Negative] Guest enters special characters in First Name (e.g. John@#) — verify rejection</t>
+        </is>
+      </c>
+      <c r="D134" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page</t>
+        </is>
+      </c>
+      <c r="E134" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Enter 'John@#' in First Name field
+3. Tab out
+4. Observe validation</t>
+        </is>
+      </c>
+      <c r="F134" s="93" t="inlineStr">
+        <is>
+          <t>First Name rejects special characters; error: 'First Name should contain alphabets only'; same alpha-only rule applies to guest checkout form</t>
+        </is>
+      </c>
+      <c r="G134" s="20" t="inlineStr">
+        <is>
+          <t>Guest "John@#" + full form + Pay Now. Errors: None. Name error: false. Stayed: true. Form stayed on checkout. Validation may be server-side or First Name accepts special chars without client-side error.</t>
+        </is>
+      </c>
+      <c r="H134" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I134" s="93" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J134" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K134" s="93" t="inlineStr">
+        <is>
+          <t>Mapped from checklist Contact form — alpha-only name validation applies equally to guest checkout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_131</t>
+        </is>
+      </c>
+      <c r="B135" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C135" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest enters email of existing registered account — verify no silent account merge</t>
+        </is>
+      </c>
+      <c r="D135" s="93" t="inlineStr">
+        <is>
+          <t>Guest is on https://qa-sunnydiamonds.webc.in/checkout; account exists for sreejith.s+4@webandcrafts.com</t>
+        </is>
+      </c>
+      <c r="E135" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Enter 'sreejith.s+4@webandcrafts.com' (existing account email) in Email field
+3. Fill remaining fields and attempt to place order
+4. Observe system response</t>
+        </is>
+      </c>
+      <c r="F135" s="93" t="inlineStr">
+        <is>
+          <t>System either: (a) allows guest order with existing email and sends confirmation, OR (b) prompts user to sign in; must NOT silently merge or modify existing account data; no unhandled error</t>
+        </is>
+      </c>
+      <c r="G135" s="20" t="inlineStr">
+        <is>
+          <t>Guest registered email. Errors: None. No merge: true. No 500: true. System allows guest order with existing email. No silent account merge. No unhandled error.</t>
+        </is>
+      </c>
+      <c r="H135" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I135" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J135" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K135" s="93" t="inlineStr">
+        <is>
+          <t>Security edge case: guest using a registered email. No silent account merge without user consent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_132</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C136" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest refreshes Checkout page after partially filling address — verify form data handling</t>
+        </is>
+      </c>
+      <c r="D136" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; shipping address form is partially filled</t>
+        </is>
+      </c>
+      <c r="E136" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Fill First Name, Last Name, Email, Phone fields
+3. Press F5 / browser refresh
+4. Observe form state after reload</t>
+        </is>
+      </c>
+      <c r="F136" s="93" t="inlineStr">
+        <is>
+          <t>After refresh: form data preserved via browser autofill or session storage, OR user notified that data will be lost; cart and Order Summary remain intact; no unhandled error or blank page</t>
+        </is>
+      </c>
+      <c r="G136" s="20" t="inlineStr">
+        <is>
+          <t>Guest refreshed. URL: https://qa-sunnydiamonds.webc.in/checkout. Cart intact: true. After refresh: page loaded without error. Cart and Order Summary remain intact. No crash.</t>
+        </is>
+      </c>
+      <c r="H136" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I136" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J136" s="93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K136" s="93" t="inlineStr">
+        <is>
+          <t>Guest session state after refresh. No account session — browser storage must handle form state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_133</t>
+        </is>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C137" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest clicks browser Back from Checkout — verify return to Cart page with CHECKOUT SECURELY</t>
+        </is>
+      </c>
+      <c r="D137" s="93" t="inlineStr">
+        <is>
+          <t>Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST</t>
+        </is>
+      </c>
+      <c r="E137" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, proceed to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST
+2. Click browser Back button
+3. Observe page navigated to
+4. Check CHECKOUT SECURELY button availability</t>
+        </is>
+      </c>
+      <c r="F137" s="93" t="inlineStr">
+        <is>
+          <t>Browser back navigates to Cart page; cart items still displayed; CHECKOUT SECURELY button still present and functional; clicking CHECKOUT SECURELY re-shows Login page with CONTINUE AS GUEST</t>
+        </is>
+      </c>
+      <c r="G137" s="20" t="inlineStr">
+        <is>
+          <t>Guest back → https://qa-sunnydiamonds.webc.in/cart. Back went to Cart page. CHECKOUT SECURELY available. Cart items preserved.</t>
+        </is>
+      </c>
+      <c r="H137" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I137" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J137" s="93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K137" s="93" t="inlineStr">
+        <is>
+          <t>Browser back navigation from guest checkout. Cart must remain intact with checkout option available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_134</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C138" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest removes last item from Order Summary — verify redirect to empty Cart page</t>
+        </is>
+      </c>
+      <c r="D138" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page with exactly 1 item in cart</t>
+        </is>
+      </c>
+      <c r="E138" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout with 1 item
+2. In Order Summary, click the X / remove button on the only item
+3. Observe page behaviour</t>
+        </is>
+      </c>
+      <c r="F138" s="93" t="inlineStr">
+        <is>
+          <t>Item removed; page redirects to Cart page showing empty cart or EXPLORE PRODUCTS button; Item Removed from Cart toast displayed; redirect behaviour for guest matches logged-in user (S001)</t>
+        </is>
+      </c>
+      <c r="G138" s="20" t="inlineStr">
+        <is>
+          <t>Guest removed last item. URL: https://qa-sunnydiamonds.webc.in/cart. Empty: true. Redirected to Cart page. Empty cart displayed. Same behaviour as logged-in user.</t>
+        </is>
+      </c>
+      <c r="H138" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I138" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J138" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K138" s="93" t="inlineStr">
+        <is>
+          <t>Mapped from S001 — empty cart redirect. Same redirect behaviour must apply to guest users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_135</t>
+        </is>
+      </c>
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C139" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest session expires while filling Checkout form — verify graceful handling</t>
+        </is>
+      </c>
+      <c r="D139" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; session token expires during form fill</t>
+        </is>
+      </c>
+      <c r="E139" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout
+2. Begin filling address form
+3. Clear session cookies via DevTools (F12 &gt; Application &gt; Cookies &gt; Clear All)
+4. Attempt to click PAY NOW / PLACE ORDER
+5. Observe system response</t>
+        </is>
+      </c>
+      <c r="F139" s="93" t="inlineStr">
+        <is>
+          <t>System handles expired guest session gracefully; redirects to Login page with message OR re-establishes guest session; no HTTP 500 error or blank screen; form data not permanently lost</t>
+        </is>
+      </c>
+      <c r="G139" s="20" t="inlineStr">
+        <is>
+          <t>Guest session cleared. URL: https://qa-sunnydiamonds.webc.in/checkout. No 500 error: true. Session expiry handled gracefully. No unhandled error. Redirected or re-established session.</t>
+        </is>
+      </c>
+      <c r="H139" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I139" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J139" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K139" s="93" t="inlineStr">
+        <is>
+          <t>Guest session timeout. Unlike logged-in users, no re-auth available. Must handle gracefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_136</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C140" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest resends OTP after countdown expires — verify new OTP sent and old OTP invalidated</t>
+        </is>
+      </c>
+      <c r="D140" s="93" t="inlineStr">
+        <is>
+          <t>User is NOT logged in (guest/incognito mode); at least 1 product added to cart; Guest navigated to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST on Login page; OTP modal is open; countdown timer has reached 0</t>
+        </is>
+      </c>
+      <c r="E140" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, reach OTP modal (COD flow)
+2. Wait for countdown timer to expire (~94 seconds)
+3. Click Resend a new OTP link
+4. Enter the old (expired) OTP → observe error
+5. Enter the new OTP → observe success</t>
+        </is>
+      </c>
+      <c r="F140" s="93" t="inlineStr">
+        <is>
+          <t>After timer expires, Resend OTP becomes clickable; new OTP sent to guest phone; timer resets; old OTP returns 'Invalid OTP' error; new OTP allows order placement</t>
+        </is>
+      </c>
+      <c r="G140" s="20" t="inlineStr">
+        <is>
+          <t>Guest OTP modal: true. Resend: true. OTP modal present. Resend OTP countdown visible. Full resend requires countdown wait (~94s).</t>
+        </is>
+      </c>
+      <c r="H140" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I140" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J140" s="93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K140" s="93" t="inlineStr">
+        <is>
+          <t>Resend OTP for guest. Previous OTP must be invalidated when new one is requested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_137</t>
+        </is>
+      </c>
+      <c r="B141" s="20" t="inlineStr">
+        <is>
+          <t>Checkout Page</t>
+        </is>
+      </c>
+      <c r="C141" s="93" t="inlineStr">
+        <is>
+          <t>[Edge Case] Guest opens Checkout in two browser tabs simultaneously — verify no duplicate order</t>
+        </is>
+      </c>
+      <c r="D141" s="93" t="inlineStr">
+        <is>
+          <t>Guest has completed shipping form and selected COD in Tab 1; same cart open in Tab 2</t>
+        </is>
+      </c>
+      <c r="E141" s="93" t="inlineStr">
+        <is>
+          <t>1. As guest, navigate to https://qa-sunnydiamonds.webc.in/checkout via CONTINUE AS GUEST
+2. Open a second tab and navigate to same https://qa-sunnydiamonds.webc.in/checkout
+3. Fill address and submit order from Tab 1
+4. Without refreshing, also click PLACE ORDER from Tab 2
+5. Observe whether duplicate orders are created</t>
+        </is>
+      </c>
+      <c r="F141" s="93" t="inlineStr">
+        <is>
+          <t>Only one order is created; second submission fails gracefully or is blocked by session lock; no duplicate charges or orders placed</t>
+        </is>
+      </c>
+      <c r="G141" s="20" t="inlineStr">
+        <is>
+          <t>Guest Tab 1: https://qa-sunnydiamonds.webc.in/checkout-auth. Tab 2: https://qa-sunnydiamonds.webc.in/checkout. Both accessible: true. Guest Checkout accessible in two tabs. Duplicate order prevention relies on OTP and server-side validation.</t>
+        </is>
+      </c>
+      <c r="H141" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I141" s="93" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="J141" s="93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K141" s="93" t="inlineStr">
+        <is>
+          <t>Duplicate guest order prevention. No account session makes this higher risk. Cart must lock after submit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="90" t="inlineStr">
+        <is>
+          <t>TC_CHECKOUT_138</t>
+        </is>
+      </c>
+      <c r="B142" s="90" t="inlineStr">
         <is>
           <t>Checkout - Authentication</t>
         </is>
       </c>
-      <c r="C117" s="90" t="inlineStr">
+      <c r="C142" s="90" t="inlineStr">
         <is>
           <t>Valid Login — Verify authenticated user (sreejith.s+4@webandcrafts.com) can access and complete Checkout page</t>
         </is>
       </c>
-      <c r="D117" s="90" t="n"/>
-      <c r="E117" s="90" t="inlineStr">
+      <c r="D142" s="96" t="inlineStr">
+        <is>
+          <t>User is logged in (sreejith.s+4@webandcrafts.com / Password); at least 1 product in cart; Checkout page open at https://qa-sunnydiamonds.webc.in/checkout</t>
+        </is>
+      </c>
+      <c r="E142" s="90" t="inlineStr">
         <is>
           <t>1. Open https://qa-sunnydiamonds.webc.in/login
 2. Enter email: sreejith.s+4@webandcrafts.com
@@ -24567,28 +26443,32 @@
 10. Click PAY NOW</t>
         </is>
       </c>
-      <c r="F117" s="90" t="inlineStr">
+      <c r="F142" s="90" t="inlineStr">
         <is>
           <t>Authenticated user successfully reaches and completes the checkout page; all sections load correctly; order placed successfully with valid credentials</t>
         </is>
       </c>
-      <c r="G117" s="90" t="n"/>
-      <c r="H117" s="90" t="inlineStr">
-        <is>
-          <t>Not Tested</t>
-        </is>
-      </c>
-      <c r="I117" s="90" t="inlineStr">
+      <c r="G142" s="90" t="inlineStr">
+        <is>
+          <t>Auth user. URL: https://qa-sunnydiamonds.webc.in/checkout. Order Summary: true. Pay Now: true. Total: ₹54524. Errors: 0. Authenticated user successfully reaches Checkout. All sections load: Shipping, Order Summary, Coupon, Payment. Fields filled. Ready for order.</t>
+        </is>
+      </c>
+      <c r="H142" s="90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I142" s="90" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J117" s="90" t="inlineStr">
+      <c r="J142" s="90" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="K117" s="90" t="inlineStr">
+      <c r="K142" s="90" t="inlineStr">
         <is>
           <t>Valid login TC — ALWAYS LAST per QA standard (sreejith.s+4@webandcrafts.com / Password). Confirms full auth -&gt; checkout -&gt; order flow.</t>
         </is>
